--- a/census-regions.xlsx
+++ b/census-regions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\modern-excel-demo-day-america250\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E800B817-9F37-4029-BD18-C7F26AE7B3DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94D4B65-9305-4381-808B-A301403F1744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
   <si>
     <t>Alabama</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>division</t>
+  </si>
+  <si>
+    <t>Dist. of Columbia</t>
   </si>
 </sst>
 </file>
@@ -280,6 +283,18 @@
   </cellStyles>
   <dxfs count="5">
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -298,18 +313,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -324,12 +327,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F213E405-4DC3-44E0-8333-A128C62F88F1}" name="Table1" displayName="Table1" ref="A1:C51" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:C51" xr:uid="{F213E405-4DC3-44E0-8333-A128C62F88F1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F213E405-4DC3-44E0-8333-A128C62F88F1}" name="Table1" displayName="Table1" ref="A1:C52" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:C52" xr:uid="{F213E405-4DC3-44E0-8333-A128C62F88F1}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9C1600C3-522D-42FF-BC80-D7E9D69C7CA0}" name="state" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{34B43193-9CAC-41D2-84EE-AE157C16B98E}" name="region" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{A35B0A74-3717-4511-BFF7-940AFF234E96}" name="division" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{9C1600C3-522D-42FF-BC80-D7E9D69C7CA0}" name="state" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{34B43193-9CAC-41D2-84EE-AE157C16B98E}" name="region" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{A35B0A74-3717-4511-BFF7-940AFF234E96}" name="division" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -598,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="2" max="2" width="14.234375" customWidth="1"/>
@@ -649,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="43" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -695,7 +698,7 @@
     </row>
     <row r="9" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>1</v>
@@ -704,9 +707,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>1</v>
@@ -715,9 +718,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>1</v>
@@ -728,40 +731,40 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A14" s="2" t="s">
+    <row r="15" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A15" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A15" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>22</v>
@@ -770,20 +773,20 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="43" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="43" x14ac:dyDescent="0.5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A17" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>22</v>
@@ -792,377 +795,388 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="43" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="B19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="B22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A23" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A23" s="2" t="s">
+    <row r="24" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A24" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A24" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A25" s="2" t="s">
+    <row r="26" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A26" s="2" t="s">
+    <row r="27" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A27" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A27" s="2" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A28" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A28" s="2" t="s">
+    <row r="29" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A29" s="2" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A30" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="B30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A30" s="2" t="s">
+    <row r="31" spans="1:3" ht="43" x14ac:dyDescent="0.5">
+      <c r="A31" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A31" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A32" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A34" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A34" s="2" t="s">
+    <row r="35" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A35" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="B35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A35" s="2" t="s">
+    <row r="36" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A36" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A36" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A37" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A37" s="2" t="s">
+    <row r="38" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A38" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="B38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A38" s="2" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A39" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="B39" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A39" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A40" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A42" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="B42" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A42" s="2" t="s">
+    <row r="43" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A43" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B43" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A43" s="2" t="s">
+    <row r="44" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A44" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="B44" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A44" s="2" t="s">
+    <row r="45" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A45" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="B45" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A45" s="2" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A46" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="B46" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A46" s="2" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A47" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A47" s="2" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A48" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="B48" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A48" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A49" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A50" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="B50" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="43" x14ac:dyDescent="0.5">
-      <c r="A50" s="2" t="s">
+    <row r="51" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A51" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A51" s="2" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A52" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="B52" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>7</v>
       </c>
     </row>
